--- a/data/point-vs-interval-estimation--home_sales.xlsx
+++ b/data/point-vs-interval-estimation--home_sales.xlsx
@@ -8455,7 +8455,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: closed home-sale records, the kind a county assessor or MLS export produces.</t>
+          <t>WHAT IS CAPTURED: closed home-sale records, the kind a county assessor or MLS export produces (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sale_price is right-skewed, so also compare the mean to the median.</t>
+          <t>Compare the mean to the median: these prices are roughly symmetric, though sale prices in many markets are right-skewed.</t>
         </is>
       </c>
     </row>
